--- a/MissingReferences.xlsx
+++ b/MissingReferences.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="1196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="1126">
   <si>
     <t xml:space="preserve">Articles</t>
   </si>
@@ -217,9 +217,6 @@
   <si>
     <t xml:space="preserve">[38] CHERNIGOVSKII, V. N.: Interoceptors. American Psychological Association,
 Washington. 1967.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[41] Kinosita, Haruo. 'Studies on the Mechanism of Pigment Migration within Fish Melanophores with Special Reference to Their Electric Potentials.' (1953). </t>
   </si>
   <si>
     <t xml:space="preserve">[42] LAPAYEV, E. V., UDALOV, Yu. F., and KHALATOV, O. P.: The
@@ -2220,7 +2217,6 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">[08] Campbell PI, al-Mahrouq HA, Abraham MI, Kempson SA. Specific inhibition of rat renal Naﺘ</t>
     </r>
@@ -2229,7 +2225,6 @@
         <sz val="10"/>
         <rFont val="Microsoft YaHei"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">梲顚� </t>
     </r>
@@ -2238,7 +2233,6 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">cotransport by picolinamide. J Pharmacol Exp Ther. 1989 Oct;251(1):188-92. PMID: 2529366. </t>
     </r>
@@ -2850,9 +2844,6 @@
     <t xml:space="preserve">[14] Felipo V, Hermenegildo C, Montoliu C, Llansola M, Mi'ana MD. Neurotoxicity of ammonia and glutamate: molecular mechanisms and prevention. Neurotoxicology. 1998 Aug-Oct;19(4-5):675-81. PMID: 9745928. </t>
   </si>
   <si>
-    <t xml:space="preserve">[16] Gourdon I, Gu'rin MC, Torreilles J. Modulation de l'activit' respiratoire des macrophages r'naux du loup (Dicentrarchus labrax) par exposition chronique ' des concentrations subl'tales d'ammoniaque [Modulation of respiratory activity of renal macrophages in sea bass (Dicentrarchus labrax) by chronic exposure to sublethal concentration of ammonia]. C R Seances Soc Biol Fil. 1997;191(4):617-25. French. PMID: 9404463. </t>
-  </si>
-  <si>
     <t xml:space="preserve">[21] Kozakiewicz J, Wrzolkowa T. Badania nad ultrastruktura tkanki ?acznej w profirii p'znej oraz zwyrodnieniu starczym sk'ry (elastosis senilis [Ultrastructure of connective tissue in porphyria cutanea tarda and elastosis senilis]. Przegl Dermatol. 1973 May-Jun;60(3):289-96. Polish. PMID: 4748069. </t>
   </si>
   <si>
@@ -2892,24 +2883,12 @@
     <t xml:space="preserve">2001-05 Cocaine babies, criminal responsibility, and </t>
   </si>
   <si>
-    <t xml:space="preserve">[01] Grieve JF. Prevention of gestational failure by high protein diet. J Reprod Med. 1974 Nov;13(5):170-4. PMID: 4427320. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[03] Huether G. Amino acid availability and brain development: effects of nutritional and metabolic inadequacies. Eur J Clin Nutr. 1989;43 Suppl 1:19-25. PMID: 2567665. </t>
-  </si>
-  <si>
     <t xml:space="preserve">[09] Mello NK, Sarnyai Z, Mendelson JH, Drieze JM, Kelly M. Acute effects of cocaine on anterior pituitary hormones in male and female rhesus monkeys. J Pharmacol Exp Ther. 1993 Aug;266(2):804-11. PMID: 8355210. </t>
   </si>
   <si>
     <t xml:space="preserve">[10] Slotkin TA. Fetal nicotine or cocaine exposure: which one is worse? J Pharmacol Exp Ther. 1998 Jun;285(3):931-45. PMID: 9618392. </t>
   </si>
   <si>
-    <t xml:space="preserve">[11] Riley EP, LaFiette MH. The effects of prenatal cocaine exposure on subsequent learning in the rat. NIDA Res Monogr. 1996;164:53-77. PMID: 8809868. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[13] de Jong G, Pattinson RC, Odendaal HJ. Influence of perinatal care on stillbirths in patients of low socio-economic class. S Afr Med J. 1988 Jul 16;74(2):53-4. PMID: 3399970. </t>
-  </si>
-  <si>
     <t xml:space="preserve">[26] Fanard A, Picazo JJ. C'mo estimular la funci'n placentaria [How to stimulate the placental function (author's transl)]. Reproduccion. 1976 Jan-Jun;3(1-2):15-25. Spanish. PMID: 1027640. </t>
   </si>
   <si>
@@ -2931,9 +2910,6 @@
     <t xml:space="preserve">[11] R�ther E, Davis L, Papousek M, Reichinger M, Reiter H, Rudolph M. Pharmakologische Beeinflussung zentraler serotonerger Mechanismen am Menschen und Auswirkungen auf den Schlaf [Pharmacological influence on central serotonergic mechanisms in man and its consequences on sleep (author's transl)]. Arzneimittelforschung. 1976;26(6):1071-3. German. PMID: 134732. </t>
   </si>
   <si>
-    <t xml:space="preserve">[14] Thase ME. Treatment issues related to sleep and depression. J Clin Psychiatry. 2000;61 Suppl 11:46-50. PMID: 10926055. </t>
-  </si>
-  <si>
     <t xml:space="preserve">2001-11 Postpartum, Premenstrual, and Seasonal S </t>
   </si>
   <si>
@@ -2952,9 +2928,6 @@
     <t xml:space="preserve">[14] R'zs's C, J'zsa R, Mess B. Inhibitory role of brain stem serotoninergic neuron system on thyroid function in rat. Endocrinol Exp. 1979 Mar;13(1):9-18. PMID: 160313. </t>
   </si>
   <si>
-    <t xml:space="preserve">[15] Anisimov VN, Zavarzina NIu, Zabezhinski? MA, Popovich IG, Anikin IV, Zimina OA, Solov'ev MV, Shtylik AV, Arutiunian AV, Oparina TI, Prokopenko VM, Khavinson VKh. Vliianie melatonina na pokazateli biologicheskogo vozrasta, prodolzhitel'nost' zhizni i razvitie spontannykh opukhole? u myshe? [The effect of melatonin on the indices of biological age, on longevity and on the development of spontaneous tumors in mice]. Vopr Onkol. 2000;46(3):311-9. Russian. PMID: 10976278. </t>
-  </si>
-  <si>
     <t xml:space="preserve">[17] Danilenko KV, Putilov AA, Russkikh GS, Duffy LK, Ebbesson SO. Diurnal and seasonal variations of melatonin and serotonin in women with seasonal affective disorder. Arctic Med Res. 1994 Jul;53(3):137-45. PMID: 7986318. </t>
   </si>
   <si>
@@ -2964,9 +2937,6 @@
     <t xml:space="preserve">2002-09 Lungs Shock Inflammation And Aging </t>
   </si>
   <si>
-    <t xml:space="preserve">[02] Ansari A, Collier J, Mohsenifar Z. Isolated reduction in single-breath diffusion capacity in young, healthy, asymptomatic women. Am J Med Sci. 1995 Dec;310(6):226-8. PMID: 7503101. </t>
-  </si>
-  <si>
     <t xml:space="preserve">[16] Kharitonov SA, Barnes PJ. Nitric oxide in exhaled air is a new marker of airway inflammation. Monaldi Arch Chest Dis. 1996 Dec;51(6):533-7. PMID: 9046169. </t>
   </si>
   <si>
@@ -3057,12 +3027,6 @@
     <t xml:space="preserve">2005 Contexts for Asthma </t>
   </si>
   <si>
-    <t xml:space="preserve">[14] Terral C, Godard P, Michel FB, Macabies J. Influence des estrog'nes sur l'histamino-lib'ration du sang total induite par des allerg'nes in vitro [Influence of estrogens on histamines liberation by whole blood induced by allergens in vitro]. C R Seances Soc Biol Fil. 1981;175(2):247-52. French. PMID: 6166357. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[25] Torreilles J, Gu'rin MC. Peut-on parler d'un stress NO? [Does nitric oxide stress exist?]. C R Seances Soc Biol Fil. 1995;189(3):389-400. French. PMID: 8521087. </t>
-  </si>
-  <si>
     <t xml:space="preserve">[40] Fehrenbach E, Northoff H. Free radicals, exercise, apoptosis, and heat shock proteins. Exerc Immunol Rev. 2001;7:66-89. PMID: 11579749. </t>
   </si>
   <si>
@@ -3105,12 +3069,6 @@
     <t xml:space="preserve">2006 Autoimmunity </t>
   </si>
   <si>
-    <t xml:space="preserve">[05] Ayres S Jr, Mihan R. Is vitamin E involved in the autoimmune mechanism? Cutis. 1978 Mar;21(3):321-5. PMID: 343998. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[09] Blank M, Mendlovic S, Fricke H, Mozes E, Talal N, Shoenfeld Y. Sex hormone involvement in the induction of experimental systemic lupus erythematosus by a pathogenic anti-DNA idiotype in naive mice. J Rheumatol. 1990 Mar;17(3):311-7. PMID: 2332851. </t>
-  </si>
-  <si>
     <t xml:space="preserve">[10] Bliznakov EG. Serotonin and its precursors as modulators of the immunological responsiveness in mice. J Med. 1980;11(2-3):81-105. PMID: 6967931. </t>
   </si>
   <si>
@@ -3120,12 +3078,6 @@
     <t xml:space="preserve">[45] Talal N, Dang H, Ahmed SA, Kraig E, Fischbach M. Interleukin 2, T cell receptor and sex hormone studies in autoimmune mice. J Rheumatol Suppl. 1987 Jun;14 Suppl 13:21-5. PMID: 3112377. </t>
   </si>
   <si>
-    <t xml:space="preserve">[46] Talal N, Ahmed SA. Sex hormones, CD5 (Lyl) B-cells, and autoimmune diseases. Isr J Med Sci. 1988 Dec;24(12):725-8. PMID: 3265707. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[48] Talal N. Sex hormones and modulation of immune response in SLE. Clin Rheum Dis. 1982 Apr;8(1):23-8. PMID: 6749398. </t>
-  </si>
-  <si>
     <t xml:space="preserve">[50] Torras H, Ferrando J, Mallolas J. Dermatitis postovulaci'n (dermatitis por progesterona) [Postovulation dermatitis (dermatitis caused by progesterone)]. Med Cutan Ibero Lat Am. 1980;8(1-3):15-21. Spanish. PMID: 7022048. </t>
   </si>
   <si>
@@ -3234,9 +3186,6 @@
     <t xml:space="preserve">[25] Voe?kov VL. Bio-fiziko-khimicheskie aspekty stareniia i dolgoletiia [Bio-physico-chemical aspects of aging and longevity]. Adv Gerontol. 2002;9:54-66. Russian. PMID: 12096439. </t>
   </si>
   <si>
-    <t xml:space="preserve">[27] Voeikov VL, Asfaramov R, Bouravleva EV, Novikov CN, Vilenskaya ND. Biophoton research in blood reveals its holistic properties. Indian J Exp Biol. 2003 May;41(5):473-82. PMID: 15244269. </t>
-  </si>
-  <si>
     <t xml:space="preserve">2011-05 Endotoxin, Stress, Depression </t>
   </si>
   <si>
@@ -3282,12 +3231,6 @@
     <t xml:space="preserve">[21] Okazaki K, Okutsu Y, Fukunaga A. [Effects of carbon dioxide (hypocapnia and hypercapnia) on tissue blood flow and oxygenation of liver, kidney and skeletal muscle in the dog]. Masui. 1989 Apr;38(4):457-64. Japanese. PMID: 2498552. </t>
   </si>
   <si>
-    <t xml:space="preserve">2014-07 Approaches to renewal </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[19] Sarroca A, Lin S, Bonanno JA. The effects of low pH and CO2 on bovine corneal lactate production. CLAO J. 1997 Oct;23(4):282-5. PMID: 9348454. </t>
-  </si>
-  <si>
     <t xml:space="preserve">2014-09 Antioxidants and formative fields Disruptor </t>
   </si>
   <si>
@@ -3312,9 +3255,6 @@
     <t xml:space="preserve">2015 Stress, inertia, aging </t>
   </si>
   <si>
-    <t xml:space="preserve">[03] Barron J, Sandman CA. Relationship of sedative-hypnotic response to self-injurious behavior and stereotypy by mentally retarded clients. Am J Ment Defic. 1983 Sep;88(2):177-86. PMID: 6638079. </t>
-  </si>
-  <si>
     <t xml:space="preserve">[22] Konturek SJ. Opiates and the gastrointestinal tract. Am J Gastroenterol. 1980 Sep;74(3):285-91. PMID: 6258423. </t>
   </si>
   <si>
@@ -3327,15 +3267,9 @@
     <t xml:space="preserve">[32] Powell-Jones K, Saunders WS, St Onge RD, Thornill JA. Skeletal muscle thermogenesis: its role in the hyperthermia of conscious rats given morphine or beta-endorphin. J Pharmacol Exp Ther. 1987 Oct;243(1):322-32. PMID: 2959769. </t>
   </si>
   <si>
-    <t xml:space="preserve">[34] Rhoads DL, Wei LX, Lin ET, Rezvani A, Way EL. Opioids and rat erythrocyte deformability. NIDA Res Monogr. 1986;75:121-4. PMID: 3123933. </t>
-  </si>
-  <si>
     <t xml:space="preserve">[35] Richardson JS, Zaleski WA. Naloxone and self-mutilation. Biol Psychiatry. 1983 Jan;18(1):99-101. doi: 10.1016/0378-1097(83)90142-8. PMID: 6299409. </t>
   </si>
   <si>
-    <t xml:space="preserve">[37] Sandman CA, Barron JL, Chicz-DeMet A, DeMet EM. Plasma B-endorphin levels in patients with self-injurious behavior and stereotypy. Am J Ment Retard. 1990 Jul;95(1):84-92. PMID: 2167106. </t>
-  </si>
-  <si>
     <t xml:space="preserve">2015-05 Urea, coherent life and forgotten or unreali </t>
   </si>
   <si>
@@ -3360,15 +3294,9 @@
     <t xml:space="preserve">[05] Carney SL, Dirks JH. Effect of parathyroid and antidiuretic hormone on water and calcium permeability in the rat collecting duct. Miner Electrolyte Metab. 1988;14(2-3):142-5. PMID: 3380069. </t>
   </si>
   <si>
-    <t xml:space="preserve">[06] https://www.ncbi.nlm.nih.gov/books/NBK279163/</t>
-  </si>
-  <si>
     <t xml:space="preserve">2015-09 Nitric oxide, degenerative processes, and </t>
   </si>
   <si>
-    <t xml:space="preserve">[04] Bonartsev AP, Slavutskaia Av, Postnikov AB, Medvedeva NA. Vliianie khronicheskogo vvedeniia aminoguanidina na reaktivnost' legochnykh sosudov u krys s monokrotalinovo? model'iu legochno? gipertenzii [Effect of chronic administration of aminoguanidine on the reactivity of pulmonary vessels in rats with monocrotaline-induced pulmonary hypertension]. Ross Fiziol Zh Im I M Sechenova. 2004 Jul;90(7):908-15. Russian. PMID: 15462215. </t>
-  </si>
-  <si>
     <t xml:space="preserve">[06] Chaves MC, Ribeiro RA, Rao VS. Possible involvement of nitric oxide in estrogen-induced uterine edema in the immature rat. Braz J Med Biol Res. 1993 Aug;26(8):853-7. PMID: 7507764. </t>
   </si>
   <si>
@@ -3387,21 +3315,9 @@
     <t xml:space="preserve">[29] Maletic SD, Dragicevic-Djokovic LM, Zikic RV, Stajn AS, Milenkovic P, Kostic MM. Effects of nitric oxide donors on energy metabolism of rat erythrocytes. J Environ Pathol Toxicol Oncol. 2000;19(4):383-90. PMID: 11213021. </t>
   </si>
   <si>
-    <t xml:space="preserve">2016-05 Comments on cancer therapy </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[06] Cohen P, Wax Y, Modan B. Seasonality in the occurrence of breast cancer. Cancer Res. 1983 Feb;43(2):892-6. PMID: 6848200. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[23] PARK WW, LEES JC. The absolute curability of cancer of the breast. Surg Gynecol Obstet. 1951 Aug;93(2):129-52. PMID: 14855258. </t>
-  </si>
-  <si>
     <t xml:space="preserve">2016-07 100 Years of Cancer Metabolism </t>
   </si>
   <si>
-    <t xml:space="preserve">[02] Sam Apple, NYT May 15,2016, on page MM64 of the Sunday Magazine. </t>
-  </si>
-  <si>
     <t xml:space="preserve">[03] Baev VI, Drukina MA, Valeeva GA, Volkova ZA. Tsiki krebsa v takniakh krys, podvergnutykh sochetannomy vozde?stviiu giperkapnii, gipoksii i okhlazhdeniia [Krebs cycle in tissue of rats subjected to combined effect of hypercapnia, hypoxia and cooling]. Ukr Biokhim Zh. 1975 May-Jun;47(3):352-7. Russian. PMID: 1216351.</t>
   </si>
   <si>
@@ -3411,36 +3327,18 @@
     <t xml:space="preserve">[17] Tagi-zade SB, Shapot VS. Vozmozhnost' osushchestvleniia Pasterovskogo 'ffekta astsitnymi rakovymi kletkami in vivo [Possibility of achieving the Pasteur effect by ascites carcinoma cells in vivo]. Vopr Med Khim. 1971 Jul-Aug;17(4):407-11. Russian. PMID: 5317626. </t>
   </si>
   <si>
-    <t xml:space="preserve">2016-09 Dangers of sadistic science Determinism </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[22] Harman D. Lipofuscin and ceroid formation: the cellular recycling system. Adv Exp Med Biol. 1989;266:3-15. doi: 10.1007/978-1-4899-5339-1_1. PMID: 2486157. </t>
-  </si>
-  <si>
     <t xml:space="preserve">2017 Adaptogenic Milk </t>
   </si>
   <si>
     <t xml:space="preserve">[02] Artus M. Etude, chez le jeune rat en croissance, des effets de l'administration d'un r'gime a base d'amidon ou de saccharose sur certains param'tres du m'tabolisme calcique [Effects of administering diets with starch or sucrose basis on certain parameters of calcium metabolism in the young, growing rat]. Ann Nutr Aliment. 1975;29(4):305-12. French. PMID: 1221903. </t>
   </si>
   <si>
-    <t xml:space="preserve">[13] Competitive Enterprise Institute https://cei.org/blog/annual-biofuel-subsidies-will hit-60-billion-2022-earth-track. </t>
-  </si>
-  <si>
     <t xml:space="preserve">[25] Pirie, N. W. "The direct use of leaf protein in human nutrition."'Chemistry &amp; Industry'61 (1942): 45-48. </t>
   </si>
   <si>
     <t xml:space="preserve">[27] Radjaipour M, Kindtner E, R'sler H, Eggstein M. Circadiane Rhythmik der Konzentrationen von Parathyrin und Calcitonin im Serum [Circadian rhythm of parathyrin and calcitonin concentrations in the serum]. J Clin Chem Clin Biochem. 1986 Mar;24(3):175-8. German. PMID: 3711800. </t>
   </si>
   <si>
-    <t xml:space="preserve">[32] Zamenhof S, Ahmad G. The effects of exogenous nutrients on growth of chick embryo brain. Growth. 1979 Sep;43(3):160-6. PMID: 510956. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2017-05 Language and Criticism of Science </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[04] Braden, Thomas W. "I'm Glad the CIA Is 'Immoral,'."'Saturday Evening Post'May 20, pg. 10-14 (1967). </t>
-  </si>
-  <si>
     <t xml:space="preserve">2017-07 Problems of Metabolic Energy and Efficiency </t>
   </si>
   <si>
@@ -3459,9 +3357,6 @@
     <t xml:space="preserve">[28] Puscas I, Coltau M, Baican M, Pasca R, Domuta G, Hecht A. Vasoconstrictive drugs increase carbonic anhydrase I in vascular smooth muscle while vasodilating drugs reduce the activity of this isozyme by a direct mechanism of action. Drugs Exp Clin Res. 2001;27(2):53-60. PMID: 11392054. </t>
   </si>
   <si>
-    <t xml:space="preserve">[30] Schwartz L, Supuran CT, Alfarouk KO. The Warburg Effect and the Hallmarks of Cancer. Anticancer Agents Med Chem. 2017;17(2):164-170. doi: 10.2174/1871520616666161031143301. PMID: 27804847. </t>
-  </si>
-  <si>
     <t xml:space="preserve">[31] Severinghaus JW. Endotoxin hyperventilation mechanisms. Crit Care Med. 1998 Sep;26(9):1481-2. Doi: 10.1097/00003246-199809000-00009. PMID: 9751579. </t>
   </si>
   <si>
@@ -3480,12 +3375,6 @@
     <t xml:space="preserve">[06] Luo H, Guo H, Xiao J, Xue Z. [Circadian variations of plasma SOD and MDA in health subjects]. Hua Xi Yi Ke Da Xue Xue Bao. 1997 Dec;28(4):401-3. Chinese. PMID: 10683957. </t>
   </si>
   <si>
-    <t xml:space="preserve">2018-05 Autism And Causality </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[08] https://www.kennedykrieger.org/overview/news/  study-finds-fever-may-lead-improved-behavior-ch  ildren-autism-spectrum-disorders</t>
-  </si>
-  <si>
     <t xml:space="preserve">2018-09 Cholesterol in Context - Part 1 </t>
   </si>
   <si>
@@ -3495,60 +3384,27 @@
     <t xml:space="preserve">2018-11 Cholesterol in Context Part 2 </t>
   </si>
   <si>
-    <t xml:space="preserve">[25] Smith EB. The relationship between plasma and tissue lipids in human atherosclerosis. Adv Lipid Res. 1974;12(0):1-49. doi: 10.1016/b978-0-12-024912-1.50008-9. PMID: 4371518. </t>
-  </si>
-  <si>
     <t xml:space="preserve">[28] SoRelle R. Death rate higher in elderly with low cholesterol. Circulation. 2001 Aug 14;104(7):E9011-3. PMID: 11505958. </t>
   </si>
   <si>
-    <t xml:space="preserve">2019 Money, progesterone &amp; life </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[23] Senie RT, Kinne DW. Menstrual timing of treatment for breast cancer. J Natl Cancer Inst Monogr. 1994;(16):85-90. PMID: 7999475. </t>
-  </si>
-  <si>
     <t xml:space="preserve">2019 Serotonin Energy, Degeneration, and Aging </t>
   </si>
   <si>
-    <t xml:space="preserve">[21] Montilla P, Montilla J, Pinilla J, Mu'oz MC. Serotonina cerebral en la respuesta del eje hipot'lamohip'fiso-adrenal a la hipoglucemia insul'nica [Brain serotonin in response to the hypothalamo-hypophyseal-adrenal system to insulin hypoglycemia]. Rev Esp Fisiol. 1988 Mar;44(1):93-7. Spanish. PMID: 2845530. </t>
-  </si>
-  <si>
     <t xml:space="preserve">[22] Nabarra B, Casanova M, Paris D, Nicole A, Toyama K, Sinet PM, Ceballos I, London J. Transgenic mice overexpressing the human Cu/Zn-SOD gene: ultrastructural studies of a premature thymic involution model of Down's syndrome (trisomy 21). Lab Invest. 1996 Mar;74(3):617-26. PMID: 8600312. </t>
   </si>
   <si>
     <t xml:space="preserve">[34] Tamarkina AD, Annenkov GA, Filippov IK, Lamchingi?n T. Effekt dozy gena tsitoplazmatichesko? superoksidismutazy (SOD-1) v 'ritrotsitakh bol'nykh s sindromon Dauna [Dosage effect of the cytoplasmic superoxide dismutase (SOD-1) gene in the erythrocytes of Down's syndrome patients]. Genetika. 1977;13(5):929-32. Russian. PMID: 147797. </t>
   </si>
   <si>
-    <t xml:space="preserve">2019-01 Receptors, or Sensitive Substance </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[01] Popular Science, May 1904, page 96. A talk by Paul Ehrlich at Johns Hopkins University, "Physical chemistry versus biology in the doctrines of immunity.' </t>
-  </si>
-  <si>
     <t xml:space="preserve">2019-03 Particles in Context </t>
   </si>
   <si>
-    <t xml:space="preserve">[05] Contemporary Problems in Science and Education Number 5, (2009) p.15-20. Influence of soybean gene EPSPS CP4 on the physiological state and reproductive functions of rats in the first two generations.</t>
-  </si>
-  <si>
     <t xml:space="preserve">[11] Huaux F. Une nouvelle voie pathologique menant a la fibrose pulmonaire induite par la silice: implication des r'ponses immunitaires suppressives [A new pathologic pathway for pulmonary fibrosis induced by silica: involvement of immunosuppressive responses]. Bull Mem Acad R Med Belg. 2009;164(5-6):240-6. French. PMID: 20666153. </t>
   </si>
   <si>
-    <t xml:space="preserve">[21] Soy diet suppresses reproductive function of rodents. Modern problems of science and education ' 6. (2008) (Annex 'Biological sciences'). C. 26. Maligin AG, Ermakova IV </t>
-  </si>
-  <si>
     <t xml:space="preserve">[23] Machado EA, Lair SV. Giant multinucleate macrophages in methyl cellulose-stimulated athymic nude mice. J Reticuloendothel Soc. 1978 May;23(5):383-7. PMID: 671424. </t>
   </si>
   <si>
-    <t xml:space="preserve">[30] What's killing America's teens? Inside CDC's new mortality report. News June 01, 2018. By Fiza Pirani, The Atlanta Journal-Constitution </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[42] AV Surov, NY Feoktistov, MV Ushakov, AV Gureeva (2010) Changing the physiological parameters of mammals feeding genetically modified ingredients of vegetable origin. Insti tution of the Russian Academy of Sciences Insti tute of Ecology and Evolution behalf of A. N. Severtsov RAS (IEE RAS) http://oagb.ru/ lib.php?txt_id=12292. Commissioned by the National Association for Genetic Safety </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[44] Udina M, Castellv' P, Moreno-Espa'a J, Navin's R, Vald's M, Forns X, Langohr K, Sol' R, Vieta E, Mart'n-Santos R. Interferon-induced depression in chronic hepatitis C: a systematic review and meta-analysis. J Clin Psychiatry. 2012 Aug;73(8):1128-38. doi: 10.4088/JCP.12r07694. PMID: 22967776. </t>
-  </si>
-  <si>
     <t xml:space="preserve">2019-05 Postpartum Depression, Brain Aging, </t>
   </si>
   <si>
@@ -3579,13 +3435,8 @@
     <t xml:space="preserve">2020-01 Contexts for Vaccinations </t>
   </si>
   <si>
-    <t xml:space="preserve">[06] Geffen, Dennis H. "The Incidence of Paralysis occurring in London Children within Four Weeks after Immunisation." (1950): 137-40. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[21] The Orkneys and Shetland: Their Past and Present State; SHETLAND UNDER SCOTTISH AND BRITISH RULE, pages 173-174. By John R. Tudor, 1883. https://archive.org/stream/orkneysshetlandt00tudo/ork neysshetlandt00tudo_djvu.txt </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[22] Wyatt HV. Provocation poliomyelitis: neglected clinical observations from 1914 to 1950. Bull Hist Med. 1981 Winter;55(4):543-57. PMID: 7039740. </t>
+    <t xml:space="preserve">[06] D. H. Geffen, ‘The incidence of paralysis occurring in London children within four weeks after immunization’, The Medical Officer, Vol 83 Iss 14, Macmillan Journals Ltd. (1950), 137–40. (edited)
+</t>
   </si>
   <si>
     <t xml:space="preserve">[25] Wyatt HV, Issues Med Ethics, 4(1) (1996): 14-15. A View From The West: Health Warning: Injections Can Endanger Health</t>
@@ -3594,75 +3445,27 @@
     <t xml:space="preserve">2020-03 Natural Order and Gilbert Ling </t>
   </si>
   <si>
-    <t xml:space="preserve">[12] Ling GN, Murphy RC. Studies on the physical state of water in living cells and model systems. II. NMR relaxation times of water protons in aqueous solutions of gelatin and oxygen-containing polymers which reduce the solvency of water for NA, sugars, and free amino acids. Physiol Chem Phys Med NMR. 1983;15(2):137-54. PMID: 6665043. </t>
-  </si>
-  <si>
     <t xml:space="preserve">[15] Parui R, Gambhir KK, Mehrotra PP. Changes in carbonic anhydrase may be the initial step of altered metabolism in hypertension. Biochem Int. 1991 Mar;23(4):779-89. PMID: 1908243. </t>
   </si>
   <si>
-    <t xml:space="preserve">2020-07 Education, a developmental process </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[01] Centre Canadien d''tudes Allemandes et Europ'ennes (CCEAE) Universit' de Montr'al, 25 octobre 2012. 'ducation et N'o-Lib'ralisme: L''conomie de l'Ignorance. Martin Beddeleem </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[02] Children's Health Defense Fund, July 21, 2020, Gates and Gov. Cuomo Take Advan tage of COVID-19 and Re-Imagine the NY Education System, Curtis Cost. https://childrenshealthdefense.org/news/gates-and gov-cuomo-take-advantage-of-covid-19-and-re-im agine-the-ny-education-system </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[04] Ivan Illich, Deschooling Society, 1970 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[07] Children's Health Defense Fund, July 30, 2020, New Censorship Czars: Tech Titans Aim to Restrict Access to Information in the Vaccine Debate. Robert F. Kennedy, Jr. https://childrenshealthdefense.org/news/the-new-c ensorship-czars-tech-titans-aim-to-call-the-shots-o n-what-the-public-is-exposed-to-in-the-vaccine-de bate/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[08] The Intercept, May 9, 2020, Screen New Deal, Naomi Klein. Https://theintercept.com/2020/05/08/andrew cuomo-eric-schmidt-coronavirus-tech-shock-d octrine/ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[09] Harvard Educational Review, 1954, 24, 86'97. The science of learning and the art of teaching. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[10] Harvard Educational Review, 1961, Vol. 31, pp. 377'398. Why We Need Teaching Machines, Skinner, B. F. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-01 Cumulative damage, degeneration, &amp; aging </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[01] Ahmad G, Zamenhof S. The effect of progesterone on brain and body growth of chick embryos. Growth. 1979 Mar;43(1):58-61. PMID: 456930. </t>
-  </si>
-  <si>
     <t xml:space="preserve">2021-03 Inflammation, adaptation, and aging </t>
   </si>
   <si>
-    <t xml:space="preserve">[03] Caplin I. Diabetes mellitus and insulin in an aspirin sensitive asthmatic. Ann Allergy. 1976 Mar;36(3):193-202. PMID: 1259204. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[15] JASMIN G. Etude de l'inflammation anaphylactoide [Study of anaphylactoid inflammation]. Rev Can Biol. 1956 Oct;15(2):107-85. French. PMID: 13371060. </t>
+    <t xml:space="preserve">[15] JASMIN G. Etude de l'inflammation anaphylactoide [Study of anaphylactoid inflammation]. Rev Can Biol. 1956 Oct;15(2):107-85. French. PMID: 13371060. . Diss. Université de Montréal,  </t>
   </si>
   <si>
     <t xml:space="preserve">[16] JASMIN G, RICHER L. Acquisitions recentes sur l'inflammation anaphylacto'de. II [Recent acquisitions on anaphylactoid inflammation. II]. Rev Can Biol. 1955 Sep;14(2):118-22. French. PMID: 13267233. </t>
   </si>
   <si>
-    <t xml:space="preserve">[27] Park SH, Kim KW, Lee YS, Baek JH, Kim MS, Lee YM, Lee MS, Kim YJ. Hypoglycemia-induced VEGF expression is mediated by intracellular Ca2 and protein kinase C signaling pathway in HepG2 human hepatoblastoma cells. Int J Mol Med. 2001 Jan;7(1):91-6. PMID: 11115615. </t>
-  </si>
-  <si>
     <t xml:space="preserve">2021-07 Estrogen, iron, degenerative aging </t>
   </si>
   <si>
     <t xml:space="preserve">[25] Solerte SB, Fioravanti M, Magri F, Spinillo A, Guaschino S, Ferrari E. Influence des hormones sexuelles sur l'h'morh'ologie et les prot'ines plasmatiques au cours du cycle menstruel [Influence of sex hormones on hemorrheology and plasma proteins during the menstrual cycle]. Rev Fr Gynecol Obstet. 1991 Feb 25;86(2 Pt 2):139-42. French. PMID: 1767163. </t>
   </si>
   <si>
-    <t xml:space="preserve">2021-09 Immunology, Ideology, Power </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[05] Jerne NK. Towards a network theory of the immune system. Ann Immunol (Paris). 1974 Jan;125C(1-2):373-89. PMID: 4142565. </t>
-  </si>
-  <si>
     <t xml:space="preserve">2022 Q1 Carcinogenic Metabolism </t>
   </si>
   <si>
-    <t xml:space="preserve">[19] Verma N, Tiku AB. Role of mTOR pathway in modulation of radiation induced bystander effects. Int J Radiat Biol. 2022;98(2):173-182. doi: 10.1080/09553002.2022.2013567. Epub 2021 Dec 16. PMID: 34855567. </t>
-  </si>
-  <si>
     <t xml:space="preserve">[24] Zhao Y, Huang H, Jia CH, Fan K, Xie T, Zhu ZY, Xie ML. Apigenin increases radiosensitivity of glioma stem cells by attenuating HIF-1?-mediated glycolysis. Med Oncol. 2021 Sep 23;38(11):131. doi: 10.1007/s12032-021-01586-8. PMID: 34554338. </t>
   </si>
   <si>
@@ -3670,21 +3473,6 @@
   </si>
   <si>
     <t xml:space="preserve">[20] Segall P. Long-term tryptophan restriction and aging in the rat. Aktuelle Gerontol. 1977 Oct;7(10):535-8. PMID: 22255. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Physiological Approach to Ovarian Cancer </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[03-A] Li, Min Hsin, and W. U. Gardner. "Experimental studies on the pathogenesis and histogenesis of ovarian tumors in mice."'Cancer Research'7.9 (1947): 549-566. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[03-B] GARDNER WU. Hormonal imbalances in tumorigenesis. Cancer Res. 1948 Sep;8(9):397-411. PMID: 18107381. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[05] KAPLAN HS. Influence of ovarian function on incidence of radiation-induced ovarian tumors in mice. J Natl Cancer Inst. 1950 Aug;11(1):125-32. PMID: 14784847. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">[13-B] T.E. Rohan, et al. Breast, Cancer Research 50, 3176-81, 1990. </t>
   </si>
   <si>
     <t xml:space="preserve">Oral Absorption of Progesterone </t>
@@ -3711,7 +3499,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -3732,21 +3519,25 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Microsoft YaHei"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFA6"/>
+        <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -3783,7 +3574,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3804,6 +3595,22 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3813,6 +3620,66 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFFA6"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -3927,13 +3794,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AT96"/>
+  <dimension ref="A1:AT94"/>
   <sheetFormatPr defaultColWidth="40.83984375" defaultRowHeight="144.55" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="1" width="40.84"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="33.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4177,160 +4044,157 @@
       <c r="AC4" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="AD4" s="1" t="s">
-        <v>79</v>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="I9" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="J9" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="K9" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="M9" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="N9" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="N9" s="1" t="s">
+      <c r="O9" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="O9" s="1" t="s">
+      <c r="P9" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -4354,2252 +4218,2247 @@
     </row>
     <row r="12" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="J12" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="J13" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="K13" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="I15" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="J15" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="K15" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="L15" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="M15" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="M15" s="1" t="s">
+      <c r="N15" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="I16" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="J16" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="K16" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C17" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="K17" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="L17" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="L17" s="1" t="s">
+      <c r="M17" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="M17" s="1" t="s">
+      <c r="N17" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="G18" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="I18" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="J18" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="K18" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="L18" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="L18" s="1" t="s">
+      <c r="M18" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="M18" s="1" t="s">
+      <c r="N18" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="F19" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="G19" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="C21" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="G21" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="H21" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="I21" s="1" t="s">
         <v>225</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="G22" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="G23" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="H23" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="J23" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="C24" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="E25" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="G25" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="H25" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="I25" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="J25" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="E26" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="F26" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="G26" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="H26" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="I26" s="1" t="s">
         <v>264</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="C27" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="E27" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="C28" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="E28" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="F28" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="G28" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="H28" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="I28" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="J28" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="K28" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="L28" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="L28" s="1" t="s">
+      <c r="M28" s="1" t="s">
         <v>283</v>
-      </c>
-      <c r="M28" s="1" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="C29" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="E29" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="F29" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="G29" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="H29" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="I29" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="J29" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="K29" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="K29" s="1" t="s">
+      <c r="L29" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="L29" s="1" t="s">
+      <c r="M29" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="M29" s="1" t="s">
+      <c r="N29" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="N29" s="1" t="s">
+      <c r="O29" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="O29" s="1" t="s">
+      <c r="P29" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="P29" s="1" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="C30" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="F30" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="G30" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="H30" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="I30" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="J30" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="K30" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="L30" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="L30" s="1" t="s">
+      <c r="M30" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="M30" s="1" t="s">
+      <c r="N30" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="N30" s="1" t="s">
+      <c r="O30" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="O30" s="1" t="s">
+      <c r="P30" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="P30" s="1" t="s">
+      <c r="Q30" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="Q30" s="1" t="s">
+      <c r="R30" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="R30" s="1" t="s">
+      <c r="S30" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="C31" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="D31" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="E31" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="F31" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="G31" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="H31" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="I31" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="J31" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="C33" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>335</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="C34" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="E34" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="F34" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="G34" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="H34" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="D35" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="D36" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="E36" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="F36" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="C37" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="D37" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="E37" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="F37" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="G37" s="1" t="s">
         <v>361</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="C38" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="D38" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="E38" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="F38" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="G38" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="H38" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="C39" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="D39" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="E39" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="F39" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="G39" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="H39" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="I39" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="I39" s="1" t="s">
+      <c r="J39" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="C40" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="D40" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="E40" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="F40" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="G40" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="H40" s="1" t="s">
         <v>387</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="C41" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="D41" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="C42" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="D42" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="E42" s="1" t="s">
         <v>396</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="D43" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="E45" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="F45" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="C46" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="E46" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="F46" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="G46" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="H46" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="I46" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="I46" s="1" t="s">
+      <c r="J46" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="J46" s="1" t="s">
+      <c r="K46" s="1" t="s">
         <v>417</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="C47" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="E47" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="F47" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="G47" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="H47" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="I47" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="I47" s="1" t="s">
+      <c r="J47" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="J47" s="1" t="s">
+      <c r="K47" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="K47" s="1" t="s">
+      <c r="L47" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="L47" s="1" t="s">
+      <c r="M47" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="M47" s="1" t="s">
+      <c r="N47" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="N47" s="1" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="C48" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="D48" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="C49" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="D49" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="E49" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="F49" s="1" t="s">
         <v>441</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="C50" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="D50" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="E50" s="1" t="s">
         <v>446</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="C51" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="D51" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="E51" s="1" t="s">
         <v>451</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="C52" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="D52" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="E52" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="F52" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="G52" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="G52" s="1" t="s">
+      <c r="H52" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="H52" s="1" t="s">
+      <c r="I52" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="I52" s="1" t="s">
+      <c r="J52" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="J52" s="1" t="s">
+      <c r="K52" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="K52" s="1" t="s">
+      <c r="L52" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="L52" s="1" t="s">
+      <c r="M52" s="1" t="s">
         <v>464</v>
-      </c>
-      <c r="M52" s="1" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="C53" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="D53" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="E53" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="F53" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="G53" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="H53" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="H53" s="1" t="s">
+      <c r="I53" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="I53" s="1" t="s">
+      <c r="J53" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="J53" s="1" t="s">
+      <c r="K53" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="K53" s="1" t="s">
+      <c r="L53" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="L53" s="1" t="s">
+      <c r="M53" s="1" t="s">
         <v>477</v>
-      </c>
-      <c r="M53" s="1" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="C54" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="D54" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="E54" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="F54" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="G54" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="G54" s="1" t="s">
+      <c r="H54" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="H54" s="1" t="s">
+      <c r="I54" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="I54" s="1" t="s">
+      <c r="J54" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="J54" s="1" t="s">
+      <c r="K54" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="K54" s="1" t="s">
+      <c r="L54" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="L54" s="1" t="s">
+      <c r="M54" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="M54" s="1" t="s">
+      <c r="N54" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="N54" s="1" t="s">
+      <c r="O54" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="O54" s="1" t="s">
+      <c r="P54" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="P54" s="1" t="s">
+      <c r="Q54" s="1" t="s">
         <v>494</v>
-      </c>
-      <c r="Q54" s="1" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="C55" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="D55" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="C56" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="D56" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="E56" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="F56" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="C57" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="D57" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="E57" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="F57" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="G57" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="G57" s="1" t="s">
+      <c r="H57" s="1" t="s">
         <v>512</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="C58" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="D58" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="E58" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="F58" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="G58" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="G58" s="1" t="s">
+      <c r="H58" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="H58" s="1" t="s">
+      <c r="I58" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="I58" s="1" t="s">
+      <c r="J58" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="J58" s="1" t="s">
+      <c r="K58" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="K58" s="1" t="s">
+      <c r="L58" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="L58" s="1" t="s">
+      <c r="M58" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="M58" s="1" t="s">
+      <c r="N58" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="N58" s="1" t="s">
+      <c r="O58" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="O58" s="1" t="s">
+      <c r="P58" s="1" t="s">
         <v>528</v>
-      </c>
-      <c r="P58" s="1" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="C59" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="D59" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="E59" s="1" t="s">
         <v>533</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="C60" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="D60" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="E60" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="F60" s="1" t="s">
         <v>539</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="C61" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="D61" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="E61" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="F61" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="G61" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="G61" s="1" t="s">
+      <c r="H61" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="H61" s="1" t="s">
+      <c r="I61" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="I61" s="1" t="s">
+      <c r="J61" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="J61" s="1" t="s">
+      <c r="K61" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="K61" s="1" t="s">
+      <c r="L61" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="L61" s="1" t="s">
+      <c r="M61" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="M61" s="1" t="s">
+      <c r="N61" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="N61" s="1" t="s">
+      <c r="O61" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="O61" s="1" t="s">
+      <c r="P61" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="P61" s="1" t="s">
+      <c r="Q61" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="Q61" s="1" t="s">
+      <c r="R61" s="1" t="s">
         <v>557</v>
-      </c>
-      <c r="R61" s="1" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="C62" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="D62" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="E62" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="F62" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="G62" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="G62" s="1" t="s">
+      <c r="H62" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="H62" s="1" t="s">
+      <c r="I62" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="I62" s="1" t="s">
+      <c r="J62" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="J62" s="1" t="s">
+      <c r="K62" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="K62" s="1" t="s">
+      <c r="L62" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="L62" s="1" t="s">
+      <c r="M62" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="M62" s="1" t="s">
+      <c r="N62" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="N62" s="1" t="s">
+      <c r="O62" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="O62" s="1" t="s">
+      <c r="P62" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="P62" s="1" t="s">
+      <c r="Q62" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="Q62" s="1" t="s">
+      <c r="R62" s="1" t="s">
         <v>575</v>
-      </c>
-      <c r="R62" s="1" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="C63" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="D63" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="E63" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="F63" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="F63" s="1" t="s">
+      <c r="G63" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="G63" s="1" t="s">
+      <c r="H63" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="H63" s="1" t="s">
+      <c r="I63" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="I63" s="1" t="s">
+      <c r="J63" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="J63" s="1" t="s">
+      <c r="K63" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="K63" s="1" t="s">
+      <c r="L63" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="L63" s="1" t="s">
+      <c r="M63" s="1" t="s">
         <v>588</v>
-      </c>
-      <c r="M63" s="1" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="C64" s="1" t="s">
         <v>591</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="C65" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="D65" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="E65" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="F65" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="F65" s="1" t="s">
+      <c r="G65" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="G65" s="1" t="s">
+      <c r="H65" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="H65" s="1" t="s">
+      <c r="I65" s="1" t="s">
         <v>600</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="C66" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="D66" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="E66" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="F66" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="F66" s="1" t="s">
+      <c r="G66" s="1" t="s">
         <v>607</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="C67" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="D67" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="E67" s="1" t="s">
         <v>612</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>614</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="C68" s="1" t="s">
+      <c r="D68" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="E68" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="E68" s="1" t="s">
+      <c r="F68" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="F68" s="1" t="s">
+      <c r="G68" s="1" t="s">
         <v>618</v>
       </c>
-      <c r="G68" s="1" t="s">
+      <c r="H68" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="H68" s="1" t="s">
+      <c r="I68" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="I68" s="1" t="s">
+      <c r="J68" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="J68" s="1" t="s">
+      <c r="K68" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="K68" s="1" t="s">
+      <c r="L68" s="1" t="s">
         <v>623</v>
-      </c>
-      <c r="L68" s="1" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="C69" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="D69" s="1" t="s">
         <v>627</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="C70" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="D70" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="E70" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="F70" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="F70" s="1" t="s">
+      <c r="G70" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="G70" s="1" t="s">
+      <c r="H70" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="H70" s="1" t="s">
+      <c r="I70" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="I70" s="1" t="s">
+      <c r="J70" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="J70" s="1" t="s">
+      <c r="K70" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="K70" s="1" t="s">
+      <c r="L70" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="L70" s="1" t="s">
+      <c r="M70" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="M70" s="1" t="s">
+      <c r="N70" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="N70" s="1" t="s">
+      <c r="O70" s="1" t="s">
         <v>642</v>
-      </c>
-      <c r="O70" s="1" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="C71" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="C71" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="D71" s="1" t="s">
+      <c r="E71" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="F71" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="F71" s="1" t="s">
+      <c r="G71" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="G71" s="1" t="s">
+      <c r="H71" s="1" t="s">
         <v>649</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="C72" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="D72" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="E72" s="1" t="s">
         <v>654</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="C73" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="D73" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="E73" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="F73" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="F73" s="1" t="s">
+      <c r="G73" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="G73" s="1" t="s">
+      <c r="H73" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="H73" s="1" t="s">
+      <c r="I73" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="I73" s="1" t="s">
+      <c r="J73" s="1" t="s">
         <v>664</v>
-      </c>
-      <c r="J73" s="1" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="C74" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="D74" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="E74" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="F74" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="F74" s="1" t="s">
+      <c r="G74" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="G74" s="1" t="s">
+      <c r="H74" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="H74" s="1" t="s">
+      <c r="I74" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="I74" s="1" t="s">
+      <c r="J74" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="J74" s="1" t="s">
+      <c r="K74" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="K74" s="1" t="s">
+      <c r="L74" s="1" t="s">
         <v>676</v>
-      </c>
-      <c r="L74" s="1" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="C75" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="D75" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="E75" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="F75" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="G75" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="G75" s="1" t="s">
+      <c r="H75" s="1" t="s">
         <v>684</v>
       </c>
-      <c r="H75" s="1" t="s">
+      <c r="I75" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="I75" s="1" t="s">
+      <c r="J75" s="1" t="s">
         <v>686</v>
-      </c>
-      <c r="J75" s="1" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>688</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="C77" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="D77" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="E77" s="1" t="s">
         <v>693</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="C78" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="D78" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="E78" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="E78" s="1" t="s">
+      <c r="F78" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="F78" s="1" t="s">
+      <c r="G78" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="G78" s="1" t="s">
+      <c r="H78" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="H78" s="1" t="s">
+      <c r="I78" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="I78" s="1" t="s">
+      <c r="J78" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="J78" s="1" t="s">
+      <c r="K78" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="K78" s="1" t="s">
+      <c r="L78" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="L78" s="1" t="s">
+      <c r="M78" s="1" t="s">
         <v>706</v>
-      </c>
-      <c r="M78" s="1" t="s">
-        <v>707</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="C79" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="D79" s="1" t="s">
         <v>710</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="E79" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="E79" s="1" t="s">
+      <c r="F79" s="1" t="s">
         <v>712</v>
       </c>
-      <c r="F79" s="1" t="s">
+      <c r="G79" s="1" t="s">
         <v>713</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>715</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="C80" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="D80" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="E80" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="E80" s="1" t="s">
+      <c r="F80" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="F80" s="1" t="s">
+      <c r="G80" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="G80" s="1" t="s">
+      <c r="H80" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="H80" s="1" t="s">
+      <c r="I80" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="I80" s="1" t="s">
+      <c r="J80" s="1" t="s">
         <v>723</v>
-      </c>
-      <c r="J80" s="1" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="C81" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="D81" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="E81" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="E81" s="1" t="s">
+      <c r="F81" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="F81" s="1" t="s">
+      <c r="G81" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="G81" s="1" t="s">
+      <c r="H81" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="H81" s="1" t="s">
+      <c r="I81" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="I81" s="1" t="s">
+      <c r="J81" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="J81" s="1" t="s">
+      <c r="K81" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="K81" s="1" t="s">
+      <c r="L81" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="L81" s="1" t="s">
+      <c r="M81" s="1" t="s">
         <v>736</v>
-      </c>
-      <c r="M81" s="1" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>738</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="C82" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="D82" s="1" t="s">
         <v>740</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="E82" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="E82" s="1" t="s">
+      <c r="F82" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="F82" s="1" t="s">
+      <c r="G82" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="G82" s="1" t="s">
+      <c r="H82" s="1" t="s">
         <v>744</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>746</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="C83" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="D83" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="D83" s="1" t="s">
+      <c r="E83" s="1" t="s">
         <v>749</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="C84" s="1" t="s">
         <v>752</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="D84" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="E84" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="E84" s="1" t="s">
+      <c r="F84" s="1" t="s">
         <v>755</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="C85" s="1" t="s">
         <v>758</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="D85" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="E85" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="E85" s="1" t="s">
+      <c r="F85" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="F85" s="1" t="s">
+      <c r="G85" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="G85" s="1" t="s">
+      <c r="H85" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="H85" s="1" t="s">
+      <c r="I85" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="I85" s="1" t="s">
+      <c r="J85" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="J85" s="1" t="s">
+      <c r="K85" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="K85" s="1" t="s">
+      <c r="L85" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="L85" s="1" t="s">
+      <c r="M85" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="M85" s="1" t="s">
+      <c r="N85" s="1" t="s">
         <v>769</v>
-      </c>
-      <c r="N85" s="1" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="C86" s="1" t="s">
         <v>772</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>773</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>774</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="C87" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="D87" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="E87" s="1" t="s">
         <v>777</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="C88" s="1" t="s">
         <v>780</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="D88" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="E88" s="1" t="s">
         <v>782</v>
       </c>
-      <c r="E88" s="1" t="s">
+      <c r="F88" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="F88" s="1" t="s">
+      <c r="G88" s="1" t="s">
         <v>784</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>786</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="C89" s="1" t="s">
         <v>787</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="D89" s="1" t="s">
         <v>788</v>
       </c>
-      <c r="D89" s="1" t="s">
+      <c r="E89" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="E89" s="1" t="s">
+      <c r="F89" s="1" t="s">
         <v>790</v>
       </c>
-      <c r="F89" s="1" t="s">
+      <c r="G89" s="1" t="s">
         <v>791</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="C90" s="1" t="s">
         <v>794</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="C91" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="D91" s="1" t="s">
         <v>798</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="E91" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="F91" s="1" t="s">
         <v>800</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>801</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>802</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>804</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="C93" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="D93" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="D93" s="1" t="s">
+      <c r="E93" s="1" t="s">
         <v>807</v>
       </c>
-      <c r="E93" s="1" t="s">
+      <c r="F93" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="F93" s="1" t="s">
+      <c r="G93" s="1" t="s">
         <v>809</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>811</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="C94" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="D94" s="1" t="s">
         <v>813</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="144.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B96" s="1" t="n">
-        <v>678</v>
       </c>
     </row>
   </sheetData>
@@ -6618,7 +6477,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:U87"/>
+  <dimension ref="A1:U81"/>
   <sheetFormatPr defaultColWidth="32.5234375" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="3" width="32.52"/>
@@ -6626,7 +6485,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
@@ -6691,10 +6550,10 @@
     </row>
     <row r="2" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
+        <v>815</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>816</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>817</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -6718,10 +6577,10 @@
     </row>
     <row r="3" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
+        <v>817</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>818</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>819</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -6745,22 +6604,22 @@
     </row>
     <row r="4" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
+        <v>819</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>820</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="4" t="s">
         <v>821</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>822</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>823</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>824</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>825</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -6780,10 +6639,10 @@
     </row>
     <row r="5" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
+        <v>825</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>826</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>827</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -6807,22 +6666,22 @@
     </row>
     <row r="6" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
+        <v>827</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>828</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>829</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>830</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>831</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>832</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>833</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -6842,10 +6701,10 @@
     </row>
     <row r="7" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
+        <v>833</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>834</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>835</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -6869,10 +6728,10 @@
     </row>
     <row r="8" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>836</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>837</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -6896,19 +6755,19 @@
     </row>
     <row r="9" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>838</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>839</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>840</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>841</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>842</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
@@ -6929,13 +6788,13 @@
     </row>
     <row r="10" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>843</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="4" t="s">
         <v>844</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>845</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -6958,19 +6817,19 @@
     </row>
     <row r="11" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>846</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>847</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>848</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>849</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>850</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
@@ -6991,19 +6850,19 @@
     </row>
     <row r="12" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
+        <v>850</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>851</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>852</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>853</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>854</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>855</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -7024,22 +6883,22 @@
     </row>
     <row r="13" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
+        <v>855</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>856</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>857</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="4" t="s">
         <v>858</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="E13" s="4" t="s">
         <v>859</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="F13" s="4" t="s">
         <v>860</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>861</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
@@ -7059,10 +6918,10 @@
     </row>
     <row r="14" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
+        <v>861</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>862</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>863</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -7086,10 +6945,10 @@
     </row>
     <row r="15" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
+        <v>863</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>864</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>865</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -7113,19 +6972,19 @@
     </row>
     <row r="16" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
+        <v>865</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>866</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="C16" s="4" t="s">
         <v>867</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="D16" s="4" t="s">
         <v>868</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="E16" s="4" t="s">
         <v>869</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>870</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -7146,13 +7005,13 @@
     </row>
     <row r="17" customFormat="false" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
+        <v>870</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>871</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="C17" s="4" t="s">
         <v>872</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>873</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -7175,25 +7034,25 @@
     </row>
     <row r="18" customFormat="false" ht="127.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
+        <v>873</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>874</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="C18" s="4" t="s">
         <v>875</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="D18" s="4" t="s">
         <v>876</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="E18" s="4" t="s">
         <v>877</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="F18" s="4" t="s">
         <v>878</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="G18" s="4" t="s">
         <v>879</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>880</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
@@ -7212,25 +7071,25 @@
     </row>
     <row r="19" customFormat="false" ht="127.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
+        <v>880</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>881</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="C19" s="4" t="s">
         <v>882</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="D19" s="4" t="s">
         <v>883</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="E19" s="4" t="s">
         <v>884</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="F19" s="4" t="s">
         <v>885</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="G19" s="4" t="s">
         <v>886</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>887</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
@@ -7249,25 +7108,25 @@
     </row>
     <row r="20" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>888</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="C20" s="4" t="s">
         <v>889</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="D20" s="4" t="s">
         <v>890</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="E20" s="4" t="s">
         <v>891</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="F20" s="4" t="s">
         <v>892</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="G20" s="4" t="s">
         <v>893</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>894</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
@@ -7286,22 +7145,22 @@
     </row>
     <row r="21" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
+        <v>894</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>895</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="C21" s="4" t="s">
         <v>896</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="D21" s="4" t="s">
         <v>897</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="E21" s="4" t="s">
         <v>898</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="F21" s="4" t="s">
         <v>899</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>900</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
@@ -7321,16 +7180,16 @@
     </row>
     <row r="22" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
+        <v>900</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>901</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="C22" s="4" t="s">
         <v>902</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="D22" s="4" t="s">
         <v>903</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>904</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
@@ -7352,13 +7211,13 @@
     </row>
     <row r="23" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
+        <v>904</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>905</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="C23" s="4" t="s">
         <v>906</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>907</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -7379,34 +7238,32 @@
       <c r="T23" s="4"/>
       <c r="U23" s="4"/>
     </row>
-    <row r="24" customFormat="false" ht="150.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="97.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
+        <v>907</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>908</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="C24" s="4" t="s">
         <v>909</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="D24" s="4" t="s">
         <v>910</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="E24" s="4" t="s">
         <v>911</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="F24" s="4" t="s">
         <v>912</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="G24" s="4" t="s">
         <v>913</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="H24" s="4" t="s">
         <v>914</v>
       </c>
-      <c r="H24" s="4" t="s">
-        <v>915</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>916</v>
-      </c>
+      <c r="I24" s="4"/>
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -7422,25 +7279,25 @@
     </row>
     <row r="25" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>917</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="D25" s="4" t="s">
         <v>918</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="E25" s="4" t="s">
         <v>919</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="F25" s="4" t="s">
         <v>920</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="G25" s="4" t="s">
         <v>921</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>922</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>923</v>
       </c>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
@@ -7459,10 +7316,10 @@
     </row>
     <row r="26" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -7486,29 +7343,21 @@
     </row>
     <row r="27" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>926</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="D27" s="4" t="s">
         <v>927</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>928</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>929</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>930</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>931</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>932</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>933</v>
-      </c>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
@@ -7525,26 +7374,24 @@
     </row>
     <row r="28" customFormat="false" ht="173.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>939</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>940</v>
-      </c>
+        <v>933</v>
+      </c>
+      <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
@@ -7560,34 +7407,32 @@
       <c r="T28" s="4"/>
       <c r="U28" s="4"/>
     </row>
-    <row r="29" customFormat="false" ht="173.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="150.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
+        <v>934</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>935</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>936</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>937</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>938</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>939</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>940</v>
+      </c>
+      <c r="H29" s="4" t="s">
         <v>941</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>942</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>943</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>944</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>945</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>946</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>947</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>948</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>949</v>
-      </c>
+      <c r="I29" s="4"/>
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -7601,19 +7446,17 @@
       <c r="T29" s="4"/>
       <c r="U29" s="4"/>
     </row>
-    <row r="30" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="97.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>952</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>953</v>
-      </c>
+        <v>944</v>
+      </c>
+      <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
@@ -7634,34 +7477,34 @@
     </row>
     <row r="31" customFormat="false" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
+        <v>945</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>946</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>949</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>951</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="J31" s="4" t="s">
         <v>954</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>955</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>956</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>957</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>958</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>959</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>960</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>961</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>962</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>963</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -7675,33 +7518,33 @@
       <c r="T31" s="4"/>
       <c r="U31" s="4"/>
     </row>
-    <row r="32" customFormat="false" ht="150.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="132.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>964</v>
+        <v>955</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>965</v>
+        <v>956</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>966</v>
+        <v>957</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>967</v>
+        <v>958</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>968</v>
+        <v>959</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>969</v>
+        <v>960</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>970</v>
+        <v>961</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>971</v>
+        <v>962</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>972</v>
+        <v>963</v>
       </c>
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
@@ -7718,28 +7561,28 @@
     </row>
     <row r="33" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>973</v>
+        <v>964</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>974</v>
+        <v>965</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>975</v>
+        <v>966</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>976</v>
+        <v>967</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>977</v>
+        <v>968</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>978</v>
+        <v>969</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>979</v>
+        <v>970</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>980</v>
+        <v>971</v>
       </c>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
@@ -7755,19 +7598,15 @@
       <c r="T33" s="4"/>
       <c r="U33" s="4"/>
     </row>
-    <row r="34" customFormat="false" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="43.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>981</v>
+        <v>972</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>982</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>983</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>984</v>
-      </c>
+        <v>973</v>
+      </c>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
@@ -7788,40 +7627,40 @@
     </row>
     <row r="35" customFormat="false" ht="173.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
+        <v>974</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>975</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>976</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>977</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>978</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>979</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>981</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>982</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>983</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>984</v>
+      </c>
+      <c r="L35" s="4" t="s">
         <v>985</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>986</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>987</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>988</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>989</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>990</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>991</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>992</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>993</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>994</v>
-      </c>
-      <c r="K35" s="4" t="s">
-        <v>995</v>
-      </c>
-      <c r="L35" s="4" t="s">
-        <v>996</v>
       </c>
       <c r="M35" s="4"/>
       <c r="N35" s="4"/>
@@ -7833,34 +7672,26 @@
       <c r="T35" s="4"/>
       <c r="U35" s="4"/>
     </row>
-    <row r="36" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>997</v>
+        <v>986</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>998</v>
+        <v>987</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>999</v>
+        <v>988</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>1000</v>
+        <v>989</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>1001</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>1002</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>1003</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>1004</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>1005</v>
-      </c>
+        <v>990</v>
+      </c>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -7876,31 +7707,31 @@
     </row>
     <row r="37" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>1006</v>
+        <v>991</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>1007</v>
+        <v>992</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>1008</v>
+        <v>993</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>1009</v>
+        <v>994</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>1010</v>
+        <v>995</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>1011</v>
+        <v>996</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>1012</v>
+        <v>997</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>1013</v>
+        <v>998</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>1014</v>
+        <v>999</v>
       </c>
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
@@ -7917,19 +7748,19 @@
     </row>
     <row r="38" customFormat="false" ht="127.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>1015</v>
+        <v>1000</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>1016</v>
+        <v>1001</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>1017</v>
+        <v>1002</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>1018</v>
+        <v>1003</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>1019</v>
+        <v>1004</v>
       </c>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
@@ -7950,28 +7781,28 @@
     </row>
     <row r="39" customFormat="false" ht="138.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>1020</v>
+        <v>1005</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>1021</v>
+        <v>1006</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>1022</v>
+        <v>1007</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>1023</v>
+        <v>1008</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>1024</v>
+        <v>1009</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>1025</v>
+        <v>1010</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>1026</v>
+        <v>1011</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>1027</v>
+        <v>1012</v>
       </c>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
@@ -7989,22 +7820,22 @@
     </row>
     <row r="40" customFormat="false" ht="138.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>1028</v>
+        <v>1013</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>1029</v>
+        <v>1014</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>1030</v>
+        <v>1015</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>1031</v>
+        <v>1016</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>1032</v>
+        <v>1017</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>1033</v>
+        <v>1018</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
@@ -8024,13 +7855,13 @@
     </row>
     <row r="41" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>1034</v>
+        <v>1019</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>1035</v>
+        <v>1020</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>1036</v>
+        <v>1021</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -8053,20 +7884,18 @@
     </row>
     <row r="42" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>1037</v>
+        <v>1022</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>1038</v>
+        <v>1023</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>1039</v>
+        <v>1024</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>1040</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>1041</v>
-      </c>
+        <v>1025</v>
+      </c>
+      <c r="E42" s="4"/>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
@@ -8086,13 +7915,13 @@
     </row>
     <row r="43" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>1042</v>
+        <v>1026</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>1043</v>
+        <v>1027</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>1044</v>
+        <v>1028</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -8115,10 +7944,10 @@
     </row>
     <row r="44" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>1045</v>
+        <v>1029</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>1046</v>
+        <v>1030</v>
       </c>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
@@ -8142,13 +7971,13 @@
     </row>
     <row r="45" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>1047</v>
+        <v>1031</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>1048</v>
+        <v>1032</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>1049</v>
+        <v>1033</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -8171,13 +8000,13 @@
     </row>
     <row r="46" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>1050</v>
+        <v>1034</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>1051</v>
+        <v>1035</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>1052</v>
+        <v>1036</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -8200,16 +8029,16 @@
     </row>
     <row r="47" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>1053</v>
+        <v>1037</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>1054</v>
+        <v>1038</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>1055</v>
+        <v>1039</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>1056</v>
+        <v>1040</v>
       </c>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
@@ -8229,15 +8058,19 @@
       <c r="T47" s="4"/>
       <c r="U47" s="4"/>
     </row>
-    <row r="48" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>1057</v>
+        <v>1041</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>1058</v>
-      </c>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
+        <v>1042</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>1044</v>
+      </c>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
@@ -8256,19 +8089,17 @@
       <c r="T48" s="4"/>
       <c r="U48" s="4"/>
     </row>
-    <row r="49" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>1059</v>
+        <v>1045</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>1060</v>
+        <v>1046</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>1061</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>1062</v>
-      </c>
+        <v>1047</v>
+      </c>
+      <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
@@ -8287,19 +8118,25 @@
       <c r="T49" s="4"/>
       <c r="U49" s="4"/>
     </row>
-    <row r="50" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>1063</v>
+        <v>1048</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>1064</v>
+        <v>1049</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>1065</v>
-      </c>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
+        <v>1050</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>1053</v>
+      </c>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
@@ -8316,34 +8153,28 @@
       <c r="T50" s="4"/>
       <c r="U50" s="4"/>
     </row>
-    <row r="51" customFormat="false" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>1066</v>
+        <v>1054</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>1067</v>
+        <v>1055</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>1068</v>
+        <v>1056</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>1069</v>
+        <v>1057</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>1070</v>
+        <v>1058</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>1071</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>1072</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>1073</v>
-      </c>
-      <c r="I51" s="4" t="s">
-        <v>1074</v>
-      </c>
+        <v>1059</v>
+      </c>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
       <c r="J51" s="4"/>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -8357,25 +8188,17 @@
       <c r="T51" s="4"/>
       <c r="U51" s="4"/>
     </row>
-    <row r="52" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>1075</v>
+        <v>1060</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>1076</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>1077</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>1078</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>1079</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>1080</v>
-      </c>
+        <v>1061</v>
+      </c>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
@@ -8394,14 +8217,12 @@
     </row>
     <row r="53" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>1081</v>
+        <v>1062</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>1083</v>
-      </c>
+        <v>1063</v>
+      </c>
+      <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
@@ -8421,16 +8242,14 @@
       <c r="T53" s="4"/>
       <c r="U53" s="4"/>
     </row>
-    <row r="54" customFormat="false" ht="162" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>1084</v>
+        <v>1064</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>1085</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>1086</v>
-      </c>
+        <v>1065</v>
+      </c>
+      <c r="C54" s="4"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
@@ -8450,14 +8269,16 @@
       <c r="T54" s="4"/>
       <c r="U54" s="4"/>
     </row>
-    <row r="55" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
-        <v>1087</v>
+        <v>1066</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>1088</v>
-      </c>
-      <c r="C55" s="4"/>
+        <v>1067</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>1068</v>
+      </c>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
@@ -8477,17 +8298,19 @@
       <c r="T55" s="4"/>
       <c r="U55" s="4"/>
     </row>
-    <row r="56" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="97.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>1089</v>
+        <v>1069</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>1090</v>
+        <v>1070</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>1091</v>
-      </c>
-      <c r="D56" s="4"/>
+        <v>1071</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>1072</v>
+      </c>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
@@ -8506,17 +8329,19 @@
       <c r="T56" s="4"/>
       <c r="U56" s="4"/>
     </row>
-    <row r="57" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="108.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>1092</v>
+        <v>1073</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>1093</v>
+        <v>1074</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>1094</v>
-      </c>
-      <c r="D57" s="4"/>
+        <v>1075</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>1076</v>
+      </c>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
@@ -8535,24 +8360,28 @@
       <c r="T57" s="4"/>
       <c r="U57" s="4"/>
     </row>
-    <row r="58" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
-        <v>1095</v>
+        <v>1077</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>1096</v>
+        <v>1078</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>1097</v>
+        <v>1079</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>1098</v>
+        <v>1080</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>1099</v>
-      </c>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
+        <v>1081</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>1082</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>1083</v>
+      </c>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
       <c r="J58" s="4"/>
@@ -8568,14 +8397,16 @@
       <c r="T58" s="4"/>
       <c r="U58" s="4"/>
     </row>
-    <row r="59" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
-        <v>1100</v>
+        <v>1084</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>1101</v>
-      </c>
-      <c r="C59" s="4"/>
+        <v>1085</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>1086</v>
+      </c>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
       <c r="F59" s="4"/>
@@ -8595,25 +8426,17 @@
       <c r="T59" s="4"/>
       <c r="U59" s="4"/>
     </row>
-    <row r="60" customFormat="false" ht="127.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
-        <v>1102</v>
+        <v>1087</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>1103</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>1104</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>1105</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>1106</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>1107</v>
-      </c>
+        <v>1088</v>
+      </c>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
@@ -8630,12 +8453,12 @@
       <c r="T60" s="4"/>
       <c r="U60" s="4"/>
     </row>
-    <row r="61" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
-        <v>1108</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>1109</v>
+        <v>1089</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>1090</v>
       </c>
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
@@ -8657,31 +8480,19 @@
       <c r="T61" s="4"/>
       <c r="U61" s="4"/>
     </row>
-    <row r="62" customFormat="false" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
-        <v>1110</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>1111</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>1113</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>1114</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>1115</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>1116</v>
-      </c>
-      <c r="H62" s="4" t="s">
-        <v>1117</v>
-      </c>
+        <v>1091</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
       <c r="I62" s="4"/>
       <c r="J62" s="4"/>
       <c r="K62" s="4"/>
@@ -8696,15 +8507,15 @@
       <c r="T62" s="4"/>
       <c r="U62" s="4"/>
     </row>
-    <row r="63" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="127.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="s">
-        <v>1118</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>1119</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>1120</v>
+        <v>1093</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>1095</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
@@ -8725,14 +8536,16 @@
       <c r="T63" s="4"/>
       <c r="U63" s="4"/>
     </row>
-    <row r="64" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="s">
-        <v>1121</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>1122</v>
-      </c>
-      <c r="C64" s="4"/>
+        <v>1096</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>1098</v>
+      </c>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
@@ -8752,12 +8565,12 @@
       <c r="T64" s="4"/>
       <c r="U64" s="4"/>
     </row>
-    <row r="65" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="s">
-        <v>1123</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>1124</v>
+        <v>1099</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>1100</v>
       </c>
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
@@ -8779,14 +8592,16 @@
       <c r="T65" s="4"/>
       <c r="U65" s="4"/>
     </row>
-    <row r="66" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="80.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="s">
-        <v>1125</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>1126</v>
-      </c>
-      <c r="C66" s="4"/>
+        <v>1101</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>1103</v>
+      </c>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
@@ -8808,14 +8623,12 @@
     </row>
     <row r="67" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="s">
-        <v>1127</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>1129</v>
-      </c>
+        <v>1104</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C67" s="4"/>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
@@ -8835,12 +8648,12 @@
       <c r="T67" s="4"/>
       <c r="U67" s="4"/>
     </row>
-    <row r="68" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="s">
-        <v>1130</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>1131</v>
+        <v>1106</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>1107</v>
       </c>
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
@@ -8862,20 +8675,18 @@
       <c r="T68" s="4"/>
       <c r="U68" s="4"/>
     </row>
-    <row r="69" customFormat="false" ht="127.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="80.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
-        <v>1132</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>1133</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>1134</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>1135</v>
-      </c>
-      <c r="E69" s="4"/>
+        <v>1108</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D69" s="4"/>
+      <c r="E69" s="7"/>
       <c r="F69" s="4"/>
       <c r="G69" s="4"/>
       <c r="H69" s="4"/>
@@ -8893,14 +8704,14 @@
       <c r="T69" s="4"/>
       <c r="U69" s="4"/>
     </row>
-    <row r="70" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="s">
-        <v>1136</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>1137</v>
-      </c>
-      <c r="C70" s="4"/>
+        <v>1111</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C70" s="7"/>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
       <c r="F70" s="4"/>
@@ -8920,31 +8731,21 @@
       <c r="T70" s="4"/>
       <c r="U70" s="4"/>
     </row>
-    <row r="71" customFormat="false" ht="138.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="s">
-        <v>1138</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>1139</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>1140</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>1141</v>
-      </c>
-      <c r="E71" s="4" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>1143</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>1144</v>
-      </c>
-      <c r="H71" s="4" t="s">
-        <v>1145</v>
-      </c>
+        <v>1113</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D71" s="7"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
       <c r="I71" s="4"/>
       <c r="J71" s="4"/>
       <c r="K71" s="4"/>
@@ -8959,12 +8760,12 @@
       <c r="T71" s="4"/>
       <c r="U71" s="4"/>
     </row>
-    <row r="72" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="s">
-        <v>1146</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>1147</v>
+        <v>1116</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>1117</v>
       </c>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
@@ -8986,16 +8787,14 @@
       <c r="T72" s="4"/>
       <c r="U72" s="4"/>
     </row>
-    <row r="73" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="s">
-        <v>1148</v>
-      </c>
-      <c r="B73" s="4" t="s">
-        <v>1149</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>1150</v>
-      </c>
+        <v>1118</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C73" s="4"/>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
       <c r="F73" s="4"/>
@@ -9015,12 +8814,12 @@
       <c r="T73" s="4"/>
       <c r="U73" s="4"/>
     </row>
-    <row r="74" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="4" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>1152</v>
+        <v>1120</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>1121</v>
       </c>
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
@@ -9042,12 +8841,12 @@
       <c r="T74" s="4"/>
       <c r="U74" s="4"/>
     </row>
-    <row r="75" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="4" t="s">
-        <v>1153</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>1154</v>
+        <v>1122</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>1123</v>
       </c>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
@@ -9069,22 +8868,16 @@
       <c r="T75" s="4"/>
       <c r="U75" s="4"/>
     </row>
-    <row r="76" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="s">
-        <v>1155</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>1156</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>1157</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>1158</v>
-      </c>
-      <c r="E76" s="4" t="s">
-        <v>1159</v>
-      </c>
+        <v>1124</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
       <c r="F76" s="4"/>
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
@@ -9102,330 +8895,11 @@
       <c r="T76" s="4"/>
       <c r="U76" s="4"/>
     </row>
-    <row r="77" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4" t="s">
-        <v>1160</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>1161</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>1162</v>
-      </c>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
-      <c r="I77" s="4"/>
-      <c r="J77" s="4"/>
-      <c r="K77" s="4"/>
-      <c r="L77" s="4"/>
-      <c r="M77" s="4"/>
-      <c r="N77" s="4"/>
-      <c r="O77" s="4"/>
-      <c r="P77" s="4"/>
-      <c r="Q77" s="4"/>
-      <c r="R77" s="4"/>
-      <c r="S77" s="4"/>
-      <c r="T77" s="4"/>
-      <c r="U77" s="4"/>
-    </row>
-    <row r="78" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4" t="s">
-        <v>1163</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>1165</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>1166</v>
-      </c>
-      <c r="E78" s="4" t="s">
-        <v>1167</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>1168</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>1169</v>
-      </c>
-      <c r="H78" s="4" t="s">
-        <v>1170</v>
-      </c>
-      <c r="I78" s="4"/>
-      <c r="J78" s="4"/>
-      <c r="K78" s="4"/>
-      <c r="L78" s="4"/>
-      <c r="M78" s="4"/>
-      <c r="N78" s="4"/>
-      <c r="O78" s="4"/>
-      <c r="P78" s="4"/>
-      <c r="Q78" s="4"/>
-      <c r="R78" s="4"/>
-      <c r="S78" s="4"/>
-      <c r="T78" s="4"/>
-      <c r="U78" s="4"/>
-    </row>
-    <row r="79" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="4" t="s">
-        <v>1171</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4"/>
-      <c r="I79" s="4"/>
-      <c r="J79" s="4"/>
-      <c r="K79" s="4"/>
-      <c r="L79" s="4"/>
-      <c r="M79" s="4"/>
-      <c r="N79" s="4"/>
-      <c r="O79" s="4"/>
-      <c r="P79" s="4"/>
-      <c r="Q79" s="4"/>
-      <c r="R79" s="4"/>
-      <c r="S79" s="4"/>
-      <c r="T79" s="4"/>
-      <c r="U79" s="4"/>
-    </row>
-    <row r="80" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="4" t="s">
-        <v>1173</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>1174</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>1175</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>1176</v>
-      </c>
-      <c r="E80" s="4" t="s">
-        <v>1177</v>
-      </c>
-      <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
-      <c r="I80" s="4"/>
-      <c r="J80" s="4"/>
-      <c r="K80" s="4"/>
-      <c r="L80" s="4"/>
-      <c r="M80" s="4"/>
-      <c r="N80" s="4"/>
-      <c r="O80" s="4"/>
-      <c r="P80" s="4"/>
-      <c r="Q80" s="4"/>
-      <c r="R80" s="4"/>
-      <c r="S80" s="4"/>
-      <c r="T80" s="4"/>
-      <c r="U80" s="4"/>
-    </row>
-    <row r="81" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="4" t="s">
-        <v>1178</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>1179</v>
-      </c>
-      <c r="C81" s="4"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
-      <c r="F81" s="4"/>
-      <c r="G81" s="4"/>
-      <c r="H81" s="4"/>
-      <c r="I81" s="4"/>
-      <c r="J81" s="4"/>
-      <c r="K81" s="4"/>
-      <c r="L81" s="4"/>
-      <c r="M81" s="4"/>
-      <c r="N81" s="4"/>
-      <c r="O81" s="4"/>
-      <c r="P81" s="4"/>
-      <c r="Q81" s="4"/>
-      <c r="R81" s="4"/>
-      <c r="S81" s="4"/>
-      <c r="T81" s="4"/>
-      <c r="U81" s="4"/>
-    </row>
-    <row r="82" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="4" t="s">
-        <v>1180</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>1181</v>
-      </c>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
-      <c r="F82" s="4"/>
-      <c r="G82" s="4"/>
-      <c r="H82" s="4"/>
-      <c r="I82" s="4"/>
-      <c r="J82" s="4"/>
-      <c r="K82" s="4"/>
-      <c r="L82" s="4"/>
-      <c r="M82" s="4"/>
-      <c r="N82" s="4"/>
-      <c r="O82" s="4"/>
-      <c r="P82" s="4"/>
-      <c r="Q82" s="4"/>
-      <c r="R82" s="4"/>
-      <c r="S82" s="4"/>
-      <c r="T82" s="4"/>
-      <c r="U82" s="4"/>
-    </row>
-    <row r="83" customFormat="false" ht="92.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="4" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>1183</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>1184</v>
-      </c>
-      <c r="D83" s="4"/>
-      <c r="E83" s="4"/>
-      <c r="F83" s="4"/>
-      <c r="G83" s="4"/>
-      <c r="H83" s="4"/>
-      <c r="I83" s="4"/>
-      <c r="J83" s="4"/>
-      <c r="K83" s="4"/>
-      <c r="L83" s="4"/>
-      <c r="M83" s="4"/>
-      <c r="N83" s="4"/>
-      <c r="O83" s="4"/>
-      <c r="P83" s="4"/>
-      <c r="Q83" s="4"/>
-      <c r="R83" s="4"/>
-      <c r="S83" s="4"/>
-      <c r="T83" s="4"/>
-      <c r="U83" s="4"/>
-    </row>
-    <row r="84" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="4" t="s">
-        <v>1185</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>1186</v>
-      </c>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
-      <c r="F84" s="4"/>
-      <c r="G84" s="4"/>
-      <c r="H84" s="4"/>
-      <c r="I84" s="4"/>
-      <c r="J84" s="4"/>
-      <c r="K84" s="4"/>
-      <c r="L84" s="4"/>
-      <c r="M84" s="4"/>
-      <c r="N84" s="4"/>
-      <c r="O84" s="4"/>
-      <c r="P84" s="4"/>
-      <c r="Q84" s="4"/>
-      <c r="R84" s="4"/>
-      <c r="S84" s="4"/>
-      <c r="T84" s="4"/>
-      <c r="U84" s="4"/>
-    </row>
-    <row r="85" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="4" t="s">
-        <v>1187</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>1189</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>1190</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>1191</v>
-      </c>
-      <c r="F85" s="4"/>
-      <c r="G85" s="4"/>
-      <c r="H85" s="4"/>
-      <c r="I85" s="4"/>
-      <c r="J85" s="4"/>
-      <c r="K85" s="4"/>
-      <c r="L85" s="4"/>
-      <c r="M85" s="4"/>
-      <c r="N85" s="4"/>
-      <c r="O85" s="4"/>
-      <c r="P85" s="4"/>
-      <c r="Q85" s="4"/>
-      <c r="R85" s="4"/>
-      <c r="S85" s="4"/>
-      <c r="T85" s="4"/>
-      <c r="U85" s="4"/>
-    </row>
-    <row r="86" customFormat="false" ht="35.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="4" t="s">
-        <v>1192</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>1193</v>
-      </c>
-      <c r="C86" s="4"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
-      <c r="F86" s="4"/>
-      <c r="G86" s="4"/>
-      <c r="H86" s="4"/>
-      <c r="I86" s="4"/>
-      <c r="J86" s="4"/>
-      <c r="K86" s="4"/>
-      <c r="L86" s="4"/>
-      <c r="M86" s="4"/>
-      <c r="N86" s="4"/>
-      <c r="O86" s="4"/>
-      <c r="P86" s="4"/>
-      <c r="Q86" s="4"/>
-      <c r="R86" s="4"/>
-      <c r="S86" s="4"/>
-      <c r="T86" s="4"/>
-      <c r="U86" s="4"/>
-    </row>
-    <row r="87" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="4" t="s">
-        <v>1194</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>1195</v>
-      </c>
-      <c r="C87" s="4"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
-      <c r="F87" s="4"/>
-      <c r="G87" s="4"/>
-      <c r="H87" s="4"/>
-      <c r="I87" s="4"/>
-      <c r="J87" s="4"/>
-      <c r="K87" s="4"/>
-      <c r="L87" s="4"/>
-      <c r="M87" s="4"/>
-      <c r="N87" s="4"/>
-      <c r="O87" s="4"/>
-      <c r="P87" s="4"/>
-      <c r="Q87" s="4"/>
-      <c r="R87" s="4"/>
-      <c r="S87" s="4"/>
-      <c r="T87" s="4"/>
-      <c r="U87" s="4"/>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B81" s="3" t="n">
+        <f aca="false">COUNTIF(B2:N76, "*")</f>
+        <v>236</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
